--- a/자료/60차시 목록(2026-10-19).xlsx
+++ b/자료/60차시 목록(2026-10-19).xlsx
@@ -1489,17 +1489,17 @@
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>소인수분해, 거듭제곱</t>
+          <t>소인수분해, 소인수, 거듭제곱</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t>소인수분해, 거듭제곱</t>
+          <t>소인수분해</t>
         </is>
       </c>
       <c r="J8" s="27" t="inlineStr">
         <is>
-          <t>소인수</t>
+          <t>소인수, 거듭제곱</t>
         </is>
       </c>
       <c r="K8" s="24" t="n"/>
